--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/findByEmail-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/findByEmail-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="60">
-  <si>
-    <t>Statement: UserRepository.findByEmail(email) – retrieves a User record by email address. Returns null if not found.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="56">
+  <si>
+    <t>Statement: UserRepository.findByEmail(email) – Retrieves a user by email address. Returns UserWithProfile if found, null otherwise. Never throws.</t>
   </si>
   <si>
     <t/>
@@ -37,7 +37,7 @@
     <t>precondition</t>
   </si>
   <si>
-    <t>Database is accessible</t>
+    <t>Database is accessible. The provided email may or may not be registered.</t>
   </si>
   <si>
     <t>Results</t>
@@ -49,7 +49,7 @@
     <t>postcondition</t>
   </si>
   <si>
-    <t>Returns UserWithProfile or null.</t>
+    <t>On match: UserWithProfile returned with result.email: "john@example.com". On no match: null returned.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,13 +64,13 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>Email existence</t>
-  </si>
-  <si>
-    <t>Email registered</t>
-  </si>
-  <si>
-    <t>Email not registered</t>
+    <t>Email registration</t>
+  </si>
+  <si>
+    <t>Registered email → UserWithProfile returned</t>
+  </si>
+  <si>
+    <t>Unregistered email → null returned</t>
   </si>
   <si>
     <t>No TC</t>
@@ -91,10 +91,10 @@
     <t>EC-1</t>
   </si>
   <si>
-    <t>email = "john@example.com"</t>
-  </si>
-  <si>
-    <t>Returns UserWithProfile</t>
+    <t>email: "john@example.com" (registered)</t>
+  </si>
+  <si>
+    <t>UserWithProfile returned with result.email: "john@example.com", result not null</t>
   </si>
   <si>
     <t>Passed</t>
@@ -103,10 +103,10 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>email = "notfound@example.com"</t>
-  </si>
-  <si>
-    <t>Returns null</t>
+    <t>email: "notfound@example.com" (not found)</t>
+  </si>
+  <si>
+    <t>null returned</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -118,19 +118,22 @@
     <t>Email length</t>
   </si>
   <si>
-    <t>email = ""</t>
-  </si>
-  <si>
-    <t>email = "a"</t>
+    <t>0 chars (empty, not found), 1 char "a" (not found)</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 Empty</t>
-  </si>
-  <si>
-    <t>BVA-2 OneChar</t>
+    <t>BVA-1 (n=0)</t>
+  </si>
+  <si>
+    <t>email: ""</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=1)</t>
+  </si>
+  <si>
+    <t>email: "a"</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -139,24 +142,9 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Registered email</t>
-  </si>
-  <si>
-    <t>Unregistered email</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>Empty email string</t>
-  </si>
-  <si>
-    <t>BVA-2</t>
-  </si>
-  <si>
-    <t>One char email</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
@@ -187,7 +175,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>AUTH-01</t>
+    <t>REPO-06</t>
   </si>
   <si>
     <t>n/a</t>
@@ -753,7 +741,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
@@ -839,7 +827,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -867,17 +855,6 @@
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -903,7 +880,7 @@
         <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>20</v>
@@ -920,10 +897,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>29</v>
@@ -940,7 +917,7 @@
         <v>37</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>29</v>
@@ -973,10 +950,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>20</v>
@@ -999,7 +976,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>25</v>
@@ -1019,7 +996,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>29</v>
@@ -1036,10 +1013,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>29</v>
@@ -1056,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>29</v>
@@ -1093,16 +1070,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1110,39 +1087,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>55</v>
-      </c>
       <c r="H2" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B3" s="1">
         <v>4</v>
@@ -1157,19 +1134,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
